--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,45 +1020,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123875695</v>
+        <v>137324832</v>
       </c>
       <c r="B5" t="n">
-        <v>107609</v>
+        <v>92883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219686</v>
+        <v>1527</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Prakttagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Steccherinum robustius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Engelbrektsholmen, Engelbrektsholmen, Nrk</t>
+          <t>Engelbrektsviken, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532469</v>
+        <v>532405</v>
       </c>
       <c r="R5" t="n">
-        <v>6571049</v>
+        <v>6571148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,22 +1085,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,16 +1126,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123875695</t>
+          <t>https://artportalen.se/Sighting/137324832</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100148992</v>
+        <v>137324834</v>
       </c>
       <c r="B6" t="n">
-        <v>101897</v>
+        <v>91735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,44 +1143,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220075</v>
+        <v>3086</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Engelbrektsholmen, Nrk</t>
+          <t>Engelbrektsviken, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532495</v>
+        <v>532405</v>
       </c>
       <c r="R6" t="n">
-        <v>6571069</v>
+        <v>6571148</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,22 +1197,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,6 +1237,237 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137324834</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123875695</v>
+      </c>
+      <c r="B7" t="n">
+        <v>107609</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Engelbrektsholmen, Engelbrektsholmen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>532469</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6571049</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Mellösa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123875695</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100148992</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Engelbrektsholmen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>532495</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6571069</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Mellösa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/100148992</t>
         </is>
@@ -1256,6 +1480,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>137324832</v>
       </c>
       <c r="B5" t="n">
-        <v>92883</v>
+        <v>92886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137324834</v>
       </c>
       <c r="B6" t="n">
-        <v>91735</v>
+        <v>91738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>137324832</v>
       </c>
       <c r="B5" t="n">
-        <v>92886</v>
+        <v>92888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137324834</v>
       </c>
       <c r="B6" t="n">
-        <v>91738</v>
+        <v>91740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>137324832</v>
       </c>
       <c r="B5" t="n">
-        <v>92888</v>
+        <v>92893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137324834</v>
       </c>
       <c r="B6" t="n">
-        <v>91740</v>
+        <v>91745</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>137324832</v>
       </c>
       <c r="B5" t="n">
-        <v>92893</v>
+        <v>92905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137324834</v>
       </c>
       <c r="B6" t="n">
-        <v>91745</v>
+        <v>91757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>137324832</v>
       </c>
       <c r="B5" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137324834</v>
       </c>
       <c r="B6" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>137324832</v>
       </c>
       <c r="B5" t="n">
-        <v>92906</v>
+        <v>92909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137324834</v>
       </c>
       <c r="B6" t="n">
-        <v>91758</v>
+        <v>91761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>137324832</v>
       </c>
       <c r="B5" t="n">
-        <v>92909</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137324834</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>91765</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
